--- a/technician_forms/003_crowdstrike_global_threat_report_form--technician_forms.xlsx
+++ b/technician_forms/003_crowdstrike_global_threat_report_form--technician_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1087,7 +1087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1205,46 +1205,46 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>cross-site_scripting</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cross-site scripting</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>threat_categories_choices</t>
+          <t>threat_impact_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>cross-site_scripting</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cross-site scripting</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>threat_categories_choices</t>
+          <t>threat_impact_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1256,46 +1256,46 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>threat_impact_choices</t>
+          <t>threat_frequency_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>threat_impact_choices</t>
+          <t>threat_frequency_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1324,12 +1324,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1341,46 +1341,46 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>threat_frequency_choices</t>
+          <t>threat_severity_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>threat_frequency_choices</t>
+          <t>threat_severity_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1409,46 +1409,46 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>threat_severity_choices</t>
+          <t>threat_status_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>threat_severity_choices</t>
+          <t>threat_status_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>dormant</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Dormant</t>
         </is>
       </c>
     </row>
@@ -1460,46 +1460,46 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>threat_status_choices</t>
+          <t>threat_source_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>dormant</t>
+          <t>network</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dormant</t>
+          <t>Network</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>threat_status_choices</t>
+          <t>threat_source_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1511,12 +1511,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>web</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Network</t>
+          <t>Web</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>usb</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>USB</t>
         </is>
       </c>
     </row>
@@ -1545,46 +1545,46 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>threat_source_choices</t>
+          <t>threat_vector_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>usb</t>
+          <t>malicious_email_attachments</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>Malicious email attachments</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>threat_source_choices</t>
+          <t>threat_vector_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>phishing_emails</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Phishing emails</t>
         </is>
       </c>
     </row>
@@ -1596,12 +1596,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>malicious_email_attachments</t>
+          <t>drive-by_download</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Malicious email attachments</t>
+          <t>Drive-by download</t>
         </is>
       </c>
     </row>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>phishing_emails</t>
+          <t>infected_website</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Phishing emails</t>
+          <t>Infected website</t>
         </is>
       </c>
     </row>
@@ -1630,46 +1630,46 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>drive-by_download</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Drive-by download</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>threat_vector_choices</t>
+          <t>threat_level_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>infected_website</t>
+          <t>level_1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Infected website</t>
+          <t>Level 1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>threat_vector_choices</t>
+          <t>threat_level_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>level_2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Level 2</t>
         </is>
       </c>
     </row>
@@ -1681,12 +1681,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>level_1</t>
+          <t>level_3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Level 1</t>
+          <t>Level 3</t>
         </is>
       </c>
     </row>
@@ -1698,12 +1698,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>level_2</t>
+          <t>level_4</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 4</t>
         </is>
       </c>
     </row>
@@ -1715,78 +1715,44 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>level_3</t>
+          <t>level_5</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>threat_level_choices</t>
+          <t>threat_comment_aware_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>level_4</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Level 4</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>threat_level_choices</t>
+          <t>threat_comment_aware_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>level_5</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>threat_comment_aware_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>threat_comment_aware_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
         <is>
           <t>False</t>
         </is>
